--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
@@ -890,10 +890,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1041,10 +1041,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1087,10 +1087,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1192,10 +1192,10 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1238,10 +1238,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>0</v>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DIEGO GREGORIO</t>
   </si>
 </sst>
 </file>
@@ -841,16 +832,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>79.48999999999999</v>
+        <v>82.05</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -867,16 +858,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>72.97</v>
+        <v>78.38</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -902,7 +893,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -928,7 +919,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -938,7 +929,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -968,29 +959,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
@@ -480,16 +480,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>95.83</v>
+      </c>
+      <c r="H2">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -643,7 +649,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -652,7 +658,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -806,16 +818,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="G2">
+        <v>95.83</v>
+      </c>
+      <c r="H2">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
@@ -859,7 +859,7 @@
         <v>82.05</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -885,7 +885,7 @@
         <v>78.38</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,7 +911,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,7 +937,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20231.xlsx
@@ -859,7 +859,7 @@
         <v>82.05</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -885,7 +885,7 @@
         <v>78.38</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,7 +911,7 @@
         <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,7 +937,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
